--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.12436202017214</v>
+        <v>9.282708828277972</v>
       </c>
       <c r="D2" t="n">
-        <v>57.66531854416048</v>
+        <v>9.370614263426079</v>
       </c>
       <c r="E2" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F2" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.80690892374438</v>
+        <v>10.20612270010846</v>
       </c>
       <c r="D3" t="n">
-        <v>63.27022231784208</v>
+        <v>10.28141112664934</v>
       </c>
       <c r="E3" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F3" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.92528637106206</v>
+        <v>8.437859035297585</v>
       </c>
       <c r="D4" t="n">
-        <v>52.52437510443191</v>
+        <v>8.535210954470186</v>
       </c>
       <c r="E4" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F4" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.87409388465982</v>
+        <v>10.21704025625722</v>
       </c>
       <c r="D5" t="n">
-        <v>63.25632066260845</v>
+        <v>10.27915210767387</v>
       </c>
       <c r="E5" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F5" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>82.07899574997923</v>
+        <v>13.33783680937163</v>
       </c>
       <c r="D6" t="n">
-        <v>82.35416698707725</v>
+        <v>13.38255213540005</v>
       </c>
       <c r="E6" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F6" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.00270685243979</v>
+        <v>8.125439863521466</v>
       </c>
       <c r="D7" t="n">
-        <v>50.50658073244657</v>
+        <v>8.207319369022569</v>
       </c>
       <c r="E7" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F7" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>67.86567670061461</v>
+        <v>11.02817246384988</v>
       </c>
       <c r="D8" t="n">
-        <v>68.32524526485986</v>
+        <v>11.10285235553973</v>
       </c>
       <c r="E8" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F8" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.27167643283983</v>
+        <v>8.331647420336472</v>
       </c>
       <c r="D9" t="n">
-        <v>51.68166440926454</v>
+        <v>8.398270466505489</v>
       </c>
       <c r="E9" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F9" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>69.12637651927315</v>
+        <v>11.23303618438189</v>
       </c>
       <c r="D10" t="n">
-        <v>69.40211042477964</v>
+        <v>11.27784294402669</v>
       </c>
       <c r="E10" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F10" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.71836275684971</v>
+        <v>10.02923394798808</v>
       </c>
       <c r="D11" t="n">
-        <v>62.03552381137045</v>
+        <v>10.0807726193477</v>
       </c>
       <c r="E11" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F11" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.13688873927524</v>
+        <v>6.684744420132226</v>
       </c>
       <c r="D12" t="n">
-        <v>41.64684020716906</v>
+        <v>6.767611533664973</v>
       </c>
       <c r="E12" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F12" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>69.82023611170743</v>
+        <v>11.34578836815246</v>
       </c>
       <c r="D13" t="n">
-        <v>70.00887802351417</v>
+        <v>11.37644267882105</v>
       </c>
       <c r="E13" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F13" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>81.28947078753062</v>
+        <v>13.20953900297373</v>
       </c>
       <c r="D14" t="n">
-        <v>81.41166717929534</v>
+        <v>13.22939591663549</v>
       </c>
       <c r="E14" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F14" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.50844513339684</v>
+        <v>5.282622334176986</v>
       </c>
       <c r="D15" t="n">
-        <v>33.04638475560841</v>
+        <v>5.370037522786368</v>
       </c>
       <c r="E15" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F15" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>70.63406891200442</v>
+        <v>11.47803619820072</v>
       </c>
       <c r="D16" t="n">
-        <v>70.6206564147015</v>
+        <v>11.47585666738899</v>
       </c>
       <c r="E16" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F16" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>21.77305860513991</v>
+        <v>3.538122023335235</v>
       </c>
       <c r="D17" t="n">
-        <v>22.01181693977955</v>
+        <v>3.576920252714177</v>
       </c>
       <c r="E17" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F17" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8.385224273797796</v>
+        <v>1.362598944492142</v>
       </c>
       <c r="D18" t="n">
-        <v>7.796387598786908</v>
+        <v>1.266912984802873</v>
       </c>
       <c r="E18" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F18" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.3952230462048</v>
+        <v>7.051723745008281</v>
       </c>
       <c r="D19" t="n">
-        <v>43.13253300593759</v>
+        <v>7.009036613464859</v>
       </c>
       <c r="E19" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F19" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>36.9618594608753</v>
+        <v>6.006302162392235</v>
       </c>
       <c r="D20" t="n">
-        <v>36.65300786694752</v>
+        <v>5.956113778378972</v>
       </c>
       <c r="E20" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F20" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>77.71775485214363</v>
+        <v>12.62913516347334</v>
       </c>
       <c r="D21" t="n">
-        <v>77.53151874554305</v>
+        <v>12.59887179615075</v>
       </c>
       <c r="E21" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F21" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>55.45737022877459</v>
+        <v>9.01182266217587</v>
       </c>
       <c r="D22" t="n">
-        <v>55.48693444290095</v>
+        <v>9.016626846971405</v>
       </c>
       <c r="E22" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F22" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>23.51842002020786</v>
+        <v>3.821743253283777</v>
       </c>
       <c r="D23" t="n">
-        <v>38.42486552295604</v>
+        <v>6.244040647480356</v>
       </c>
       <c r="E23" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F23" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>41.29668055679502</v>
+        <v>6.710710590479191</v>
       </c>
       <c r="D24" t="n">
-        <v>40.90623510851777</v>
+        <v>6.647263205134138</v>
       </c>
       <c r="E24" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F24" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>24.59746243088301</v>
+        <v>3.997087645018488</v>
       </c>
       <c r="D25" t="n">
-        <v>24.03749893409481</v>
+        <v>3.906093576790406</v>
       </c>
       <c r="E25" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F25" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>22.40835796452232</v>
+        <v>3.641358169234877</v>
       </c>
       <c r="D26" t="n">
-        <v>53.66755346726682</v>
+        <v>8.720977438430859</v>
       </c>
       <c r="E26" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F26" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>32.44811826850009</v>
+        <v>5.272819218631264</v>
       </c>
       <c r="D27" t="n">
-        <v>32.00395684819983</v>
+        <v>5.200642987832473</v>
       </c>
       <c r="E27" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F27" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>83.02958975858645</v>
+        <v>13.4923083357703</v>
       </c>
       <c r="D28" t="n">
-        <v>82.72328677806479</v>
+        <v>13.44253410143553</v>
       </c>
       <c r="E28" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F28" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>17.55509493066589</v>
+        <v>2.852702926233207</v>
       </c>
       <c r="D29" t="n">
-        <v>74.27336710022067</v>
+        <v>12.06942215378586</v>
       </c>
       <c r="E29" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F29" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>30.87543471978657</v>
+        <v>5.017258141965318</v>
       </c>
       <c r="D30" t="n">
-        <v>52.49268677132381</v>
+        <v>8.530061600340119</v>
       </c>
       <c r="E30" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F30" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>46.74590302891752</v>
+        <v>7.596209242199097</v>
       </c>
       <c r="D31" t="n">
-        <v>46.1583794388429</v>
+        <v>7.500736658811971</v>
       </c>
       <c r="E31" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F31" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>31.63346017224697</v>
+        <v>5.140437277990133</v>
       </c>
       <c r="D32" t="n">
-        <v>66.07281020071902</v>
+        <v>10.73683165761684</v>
       </c>
       <c r="E32" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F32" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>44.22297392107399</v>
+        <v>7.186233262174523</v>
       </c>
       <c r="D33" t="n">
-        <v>43.61829299777476</v>
+        <v>7.087972612138398</v>
       </c>
       <c r="E33" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F33" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>54.68733788629318</v>
+        <v>8.886692406522641</v>
       </c>
       <c r="D34" t="n">
-        <v>74.57291732993951</v>
+        <v>12.11809906611517</v>
       </c>
       <c r="E34" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F34" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>48.01488763408994</v>
+        <v>7.802419240539616</v>
       </c>
       <c r="D35" t="n">
-        <v>89.79385791051301</v>
+        <v>14.59150191045837</v>
       </c>
       <c r="E35" t="n">
-        <v>19.78801883605602</v>
+        <v>3.215553060859103</v>
       </c>
       <c r="F35" t="n">
-        <v>19.19188304812549</v>
+        <v>3.118680995320392</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
